--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -917,7 +917,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
